--- a/output/billing_report/ebm_dinas_vergleich.xlsx
+++ b/output/billing_report/ebm_dinas_vergleich.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="EBM-Papst Mulfingen" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="NK_Konditionen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Accuracy_PRE" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,8 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0&quot;%%&quot;"/>
+  </numFmts>
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,11 +37,30 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -47,6 +70,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F497D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -76,13 +114,37 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -449,7 +511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG2"/>
+  <dimension ref="A1:AK9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -485,6 +547,10 @@
     <col width="9" customWidth="1" min="31" max="31"/>
     <col width="11" customWidth="1" min="32" max="32"/>
     <col width="22" customWidth="1" min="33" max="33"/>
+    <col width="12" customWidth="1" min="34" max="34"/>
+    <col width="12" customWidth="1" min="35" max="35"/>
+    <col width="10" customWidth="1" min="36" max="36"/>
+    <col width="12" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -494,176 +560,288 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1">
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>Datenqualität — PDF-Coverage + Accuracy-Basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>PRE-Sendungen gesamt (aus bi_raw)</t>
+        </is>
+      </c>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>77  (POST: 379)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>davon mit DINAS-PDF-Match</t>
+        </is>
+      </c>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>77 / 77 (100%%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>davon nach Multi-Row-Ausschluss vergleichbar</t>
+        </is>
+      </c>
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>davon im ±5%%-Band</t>
+        </is>
+      </c>
+      <c r="S6" s="4" t="inlineStr">
+        <is>
+          <t>77 / 77 (100%% der Acc.-Basis)  ← Basis-Accuracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Ausschluss-Gründe</t>
+        </is>
+      </c>
+      <c r="S7" s="4" t="inlineStr">
+        <is>
+          <t>A) Kein DINAS-Match: 0  |  B) Sammelposten (nicht ausgeschl.): 292 (64%%)  |  C) Solo-Gutschriften: 0  |  D) DINAS Multi-Row: 0 (aus ±5%%-Basis ausgeschl.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Vergleich-Methode</t>
+        </is>
+      </c>
+      <c r="S8" s="4" t="inlineStr">
+        <is>
+          <t>Komplettpreis → DINAS total_items vs BI Erloese  |  Standard → DINAS fracht vs BI Erlöse Fracht</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
           <t>System</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Auftrags-Nr</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Master-Nr</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Sub-Nr(n)</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Anzahl Subs</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>Ist Master</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Rech.-Nr</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>Sendungsdatum</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>Kunde</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>Land</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>Empf.PLZ</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L9" s="5" t="inlineStr">
         <is>
           <t>Vers.PLZ</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="M9" s="5" t="inlineStr">
         <is>
           <t>Gew.band</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="N9" s="5" t="inlineStr">
         <is>
           <t>Zone</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="O9" s="5" t="inlineStr">
         <is>
           <t>Basis</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="P9" s="5" t="inlineStr">
         <is>
           <t>Basis Menge</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="Q9" s="5" t="inlineStr">
         <is>
           <t>Basispreis</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="R9" s="5" t="inlineStr">
         <is>
           <t>Eff. Preis</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
+      <c r="S9" s="5" t="inlineStr">
         <is>
           <t>Tonnage kg</t>
         </is>
       </c>
-      <c r="T2" s="2" t="inlineStr">
+      <c r="T9" s="5" t="inlineStr">
         <is>
           <t>Stellplätze</t>
         </is>
       </c>
-      <c r="U2" s="2" t="inlineStr">
+      <c r="U9" s="5" t="inlineStr">
         <is>
           <t>Lademeter</t>
         </is>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="V9" s="5" t="inlineStr">
         <is>
           <t>Volumen</t>
         </is>
       </c>
-      <c r="W2" s="2" t="inlineStr">
+      <c r="W9" s="5" t="inlineStr">
         <is>
           <t>Soll EUR</t>
         </is>
       </c>
-      <c r="X2" s="2" t="inlineStr">
+      <c r="X9" s="5" t="inlineStr">
         <is>
           <t>Fracht EUR</t>
         </is>
       </c>
-      <c r="Y2" s="2" t="inlineStr">
+      <c r="Y9" s="5" t="inlineStr">
         <is>
           <t>Diesel EUR</t>
         </is>
       </c>
-      <c r="Z2" s="2" t="inlineStr">
+      <c r="Z9" s="5" t="inlineStr">
         <is>
           <t>Maut EUR</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
+      <c r="AA9" s="5" t="inlineStr">
         <is>
           <t>Lademittel</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
+      <c r="AB9" s="5" t="inlineStr">
         <is>
           <t>Peak EUR</t>
         </is>
       </c>
-      <c r="AC2" s="2" t="inlineStr">
+      <c r="AC9" s="5" t="inlineStr">
         <is>
           <t>Neben EUR</t>
         </is>
       </c>
-      <c r="AD2" s="2" t="inlineStr">
+      <c r="AD9" s="5" t="inlineStr">
         <is>
           <t>EUST Zoll</t>
         </is>
       </c>
-      <c r="AE2" s="2" t="inlineStr">
+      <c r="AE9" s="5" t="inlineStr">
         <is>
           <t>Versich.</t>
         </is>
       </c>
-      <c r="AF2" s="2" t="inlineStr">
+      <c r="AF9" s="5" t="inlineStr">
         <is>
           <t>Erlöse</t>
         </is>
       </c>
-      <c r="AG2" s="2" t="inlineStr">
+      <c r="AG9" s="5" t="inlineStr">
         <is>
           <t>Abw. Grund</t>
         </is>
       </c>
+      <c r="AH9" s="5" t="inlineStr">
+        <is>
+          <t>Komplettpreis</t>
+        </is>
+      </c>
+      <c r="AI9" s="5" t="inlineStr">
+        <is>
+          <t>BI-Split</t>
+        </is>
+      </c>
+      <c r="AJ9" s="5" t="inlineStr">
+        <is>
+          <t>DINAS vs BI %</t>
+        </is>
+      </c>
+      <c r="AK9" s="5" t="inlineStr">
+        <is>
+          <t>DINAS Multi-Row</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AG1"/>
+  <mergeCells count="14">
+    <mergeCell ref="A3:R3"/>
+    <mergeCell ref="S7:AK7"/>
+    <mergeCell ref="S5:AK5"/>
+    <mergeCell ref="A7:R7"/>
+    <mergeCell ref="S6:AK6"/>
+    <mergeCell ref="A2:R2"/>
+    <mergeCell ref="S4:AK4"/>
+    <mergeCell ref="S3:AK3"/>
+    <mergeCell ref="S8:AK8"/>
+    <mergeCell ref="A5:R5"/>
+    <mergeCell ref="A1:AK1"/>
+    <mergeCell ref="A8:R8"/>
+    <mergeCell ref="A6:R6"/>
+    <mergeCell ref="A4:R4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -691,4 +869,4610 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P79"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>EBM-Papst Mulfingen GmbH &amp; Co. KG (410844) — PRE Accuracy: DINAS Total vs BI Erloese_effektiv  |  Rows: 77  |  Multi-Row (ausgeschl.): 0  |  Acc.-Basis: 77  |  ±5%%: 77 (100%% der Basis)  |  &gt;10%% Abw.: 0  |  Komplettpreis: 77  |  Sammelposten: 4  |  Solo-Gutschrift: 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Auftrags-Nr</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Rech.-Nr DINAS</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Rech.-Nr BI</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Datum</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Land</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>Empf.PLZ</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Tonnage kg</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>DINAS Total/Fracht</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>BI Erloese_eff</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Diff EUR</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Diff %%</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>Komplettpreis</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>BI-Split</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Solo-Gutschrift</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>Multi-Row DINAS</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr">
+        <is>
+          <t>Abw. Klasse</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>32899306</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>3766862</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="n">
+        <v>45800</v>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAL      </t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="n">
+        <v>10739</v>
+      </c>
+      <c r="H3" s="9" t="n">
+        <v>3569.19</v>
+      </c>
+      <c r="I3" s="9" t="n">
+        <v>3683.23</v>
+      </c>
+      <c r="J3" s="9" t="n">
+        <v>-114.04</v>
+      </c>
+      <c r="K3" s="10" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="N3" s="7" t="inlineStr"/>
+      <c r="O3" s="7" t="inlineStr"/>
+      <c r="P3" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>32899300</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>3766861</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>3766861</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>45800</v>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LAO      </t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>4258</v>
+      </c>
+      <c r="H4" s="9" t="n">
+        <v>2977.39</v>
+      </c>
+      <c r="I4" s="9" t="n">
+        <v>3071.92</v>
+      </c>
+      <c r="J4" s="9" t="n">
+        <v>-94.53</v>
+      </c>
+      <c r="K4" s="10" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M4" s="7" t="inlineStr"/>
+      <c r="N4" s="7" t="inlineStr"/>
+      <c r="O4" s="7" t="inlineStr"/>
+      <c r="P4" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>32899151</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>3766858</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>3766858</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>45799</v>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LAO      </t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>5716</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>3591</v>
+      </c>
+      <c r="I5" s="9" t="n">
+        <v>3685.53</v>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>-94.53</v>
+      </c>
+      <c r="K5" s="10" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="inlineStr"/>
+      <c r="N5" s="7" t="inlineStr"/>
+      <c r="O5" s="7" t="inlineStr"/>
+      <c r="P5" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>32899243</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>3766859</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>3766859</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>45800</v>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LAO      </t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>7631</v>
+      </c>
+      <c r="H6" s="9" t="n">
+        <v>3591</v>
+      </c>
+      <c r="I6" s="9" t="n">
+        <v>3685.53</v>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>-94.53</v>
+      </c>
+      <c r="K6" s="10" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M6" s="7" t="inlineStr"/>
+      <c r="N6" s="7" t="inlineStr"/>
+      <c r="O6" s="7" t="inlineStr"/>
+      <c r="P6" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>32899150</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>3766857</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>3766857</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>45799</v>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LAO      </t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>7245</v>
+      </c>
+      <c r="H7" s="9" t="n">
+        <v>3591</v>
+      </c>
+      <c r="I7" s="9" t="n">
+        <v>3685.53</v>
+      </c>
+      <c r="J7" s="9" t="n">
+        <v>-94.53</v>
+      </c>
+      <c r="K7" s="10" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr"/>
+      <c r="N7" s="7" t="inlineStr"/>
+      <c r="O7" s="7" t="inlineStr"/>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>32910812</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>3769102</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>3769102</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>45821</v>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LAO      </t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>7813</v>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>3570.75</v>
+      </c>
+      <c r="I8" s="9" t="n">
+        <v>3665.28</v>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>-94.53</v>
+      </c>
+      <c r="K8" s="10" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M8" s="7" t="inlineStr"/>
+      <c r="N8" s="7" t="inlineStr"/>
+      <c r="O8" s="7" t="inlineStr"/>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>32899245</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>3766860</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>3766860</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>45800</v>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LAO      </t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>5583</v>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>3591</v>
+      </c>
+      <c r="I9" s="9" t="n">
+        <v>3685.53</v>
+      </c>
+      <c r="J9" s="9" t="n">
+        <v>-94.53</v>
+      </c>
+      <c r="K9" s="10" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M9" s="7" t="inlineStr"/>
+      <c r="N9" s="7" t="inlineStr"/>
+      <c r="O9" s="7" t="inlineStr"/>
+      <c r="P9" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>32902637</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>3767982</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>3767982</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>45810</v>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LAO      </t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>5289</v>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>2960.6</v>
+      </c>
+      <c r="I10" s="9" t="n">
+        <v>3027.96</v>
+      </c>
+      <c r="J10" s="9" t="n">
+        <v>-67.36</v>
+      </c>
+      <c r="K10" s="10" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M10" s="7" t="inlineStr"/>
+      <c r="N10" s="7" t="inlineStr"/>
+      <c r="O10" s="7" t="inlineStr"/>
+      <c r="P10" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>32895900</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>3766855</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>3766855</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>45796</v>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COR      </t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>4223</v>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>3537.8</v>
+      </c>
+      <c r="I11" s="9" t="n">
+        <v>3602.42</v>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>-64.62</v>
+      </c>
+      <c r="K11" s="10" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M11" s="7" t="inlineStr"/>
+      <c r="N11" s="7" t="inlineStr"/>
+      <c r="O11" s="7" t="inlineStr"/>
+      <c r="P11" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>32906669</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>3771854</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>3771854</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>45813</v>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COR      </t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>4262</v>
+      </c>
+      <c r="H12" s="9" t="n">
+        <v>3582.47</v>
+      </c>
+      <c r="I12" s="9" t="n">
+        <v>3582.47</v>
+      </c>
+      <c r="J12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M12" s="7" t="inlineStr"/>
+      <c r="N12" s="7" t="inlineStr"/>
+      <c r="O12" s="7" t="inlineStr"/>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>32907247</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>3771855</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>3771855</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>45814</v>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LAO      </t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H13" s="9" t="n">
+        <v>3666.18</v>
+      </c>
+      <c r="I13" s="9" t="n">
+        <v>3666.18</v>
+      </c>
+      <c r="J13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M13" s="7" t="inlineStr"/>
+      <c r="N13" s="7" t="inlineStr"/>
+      <c r="O13" s="7" t="inlineStr"/>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>32909718</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>3771856</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>3771856</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>45821</v>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAL      </t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H14" s="9" t="n">
+        <v>3772.91</v>
+      </c>
+      <c r="I14" s="9" t="n">
+        <v>3772.91</v>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M14" s="7" t="inlineStr"/>
+      <c r="N14" s="7" t="inlineStr"/>
+      <c r="O14" s="7" t="inlineStr"/>
+      <c r="P14" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>32910842</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>3770531</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>3770531</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>45824</v>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DON      </t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>8000</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>3582.47</v>
+      </c>
+      <c r="I15" s="9" t="n">
+        <v>3582.47</v>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M15" s="7" t="inlineStr"/>
+      <c r="N15" s="7" t="inlineStr"/>
+      <c r="O15" s="7" t="inlineStr"/>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>32917417</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>3770540</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>3770540</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>45835</v>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAL      </t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>7291</v>
+      </c>
+      <c r="H16" s="9" t="n">
+        <v>3282.14</v>
+      </c>
+      <c r="I16" s="9" t="n">
+        <v>3282.14</v>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M16" s="7" t="inlineStr"/>
+      <c r="N16" s="7" t="inlineStr"/>
+      <c r="O16" s="7" t="inlineStr"/>
+      <c r="P16" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>32917343</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>3770541</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>3770541</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>45838</v>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LAO      </t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>3221</v>
+      </c>
+      <c r="H17" s="9" t="n">
+        <v>1350.93</v>
+      </c>
+      <c r="I17" s="9" t="n">
+        <v>1350.93</v>
+      </c>
+      <c r="J17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M17" s="7" t="inlineStr"/>
+      <c r="N17" s="7" t="inlineStr"/>
+      <c r="O17" s="7" t="inlineStr"/>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>32921332</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>3771886</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>3771886</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>45842</v>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAL      </t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>10267</v>
+      </c>
+      <c r="H18" s="9" t="n">
+        <v>3751.88</v>
+      </c>
+      <c r="I18" s="9" t="n">
+        <v>3751.88</v>
+      </c>
+      <c r="J18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M18" s="7" t="inlineStr"/>
+      <c r="N18" s="7" t="inlineStr"/>
+      <c r="O18" s="7" t="inlineStr"/>
+      <c r="P18" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>32921314</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>3771884</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>3771884</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>45842</v>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LAO      </t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>7814</v>
+      </c>
+      <c r="H19" s="9" t="n">
+        <v>3645.93</v>
+      </c>
+      <c r="I19" s="9" t="n">
+        <v>3645.93</v>
+      </c>
+      <c r="J19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M19" s="7" t="inlineStr"/>
+      <c r="N19" s="7" t="inlineStr"/>
+      <c r="O19" s="7" t="inlineStr"/>
+      <c r="P19" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>32921310</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>3771883</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>3771883</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>45842</v>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LAO      </t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>7813</v>
+      </c>
+      <c r="H20" s="9" t="n">
+        <v>3645.93</v>
+      </c>
+      <c r="I20" s="9" t="n">
+        <v>3645.93</v>
+      </c>
+      <c r="J20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M20" s="7" t="inlineStr"/>
+      <c r="N20" s="7" t="inlineStr"/>
+      <c r="O20" s="7" t="inlineStr"/>
+      <c r="P20" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>32921318</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>3771885</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>3771885</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>45842</v>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COR      </t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="n">
+        <v>4207</v>
+      </c>
+      <c r="H21" s="9" t="n">
+        <v>3562.52</v>
+      </c>
+      <c r="I21" s="9" t="n">
+        <v>3562.52</v>
+      </c>
+      <c r="J21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M21" s="7" t="inlineStr"/>
+      <c r="N21" s="7" t="inlineStr"/>
+      <c r="O21" s="7" t="inlineStr"/>
+      <c r="P21" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>32921317</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>3771692</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>3771692</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>45842</v>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LAO      </t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="n">
+        <v>7815</v>
+      </c>
+      <c r="H22" s="9" t="n">
+        <v>2115.41</v>
+      </c>
+      <c r="I22" s="9" t="n">
+        <v>2115.41</v>
+      </c>
+      <c r="J22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M22" s="7" t="inlineStr"/>
+      <c r="N22" s="7" t="inlineStr"/>
+      <c r="O22" s="7" t="inlineStr"/>
+      <c r="P22" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>32922997</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>3772399</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>3772399</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="n">
+        <v>45846</v>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAL      </t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="n">
+        <v>4079</v>
+      </c>
+      <c r="H23" s="9" t="n">
+        <v>2315.2</v>
+      </c>
+      <c r="I23" s="9" t="n">
+        <v>2315.2</v>
+      </c>
+      <c r="J23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M23" s="7" t="inlineStr"/>
+      <c r="N23" s="7" t="inlineStr"/>
+      <c r="O23" s="7" t="inlineStr"/>
+      <c r="P23" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>32925502</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>3772403</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>3772403</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>45849</v>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COR      </t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>7000</v>
+      </c>
+      <c r="H24" s="9" t="n">
+        <v>3562.52</v>
+      </c>
+      <c r="I24" s="9" t="n">
+        <v>3562.52</v>
+      </c>
+      <c r="J24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M24" s="7" t="inlineStr"/>
+      <c r="N24" s="7" t="inlineStr"/>
+      <c r="O24" s="7" t="inlineStr"/>
+      <c r="P24" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>32925494</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>3772401</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>3772401</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>45849</v>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LAO      </t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="n">
+        <v>7624</v>
+      </c>
+      <c r="H25" s="9" t="n">
+        <v>3645.93</v>
+      </c>
+      <c r="I25" s="9" t="n">
+        <v>3645.93</v>
+      </c>
+      <c r="J25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M25" s="7" t="inlineStr"/>
+      <c r="N25" s="7" t="inlineStr"/>
+      <c r="O25" s="7" t="inlineStr"/>
+      <c r="P25" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>32925489</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>3772400</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>3772400</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>45849</v>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LAO      </t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="n">
+        <v>6330</v>
+      </c>
+      <c r="H26" s="9" t="n">
+        <v>3645.93</v>
+      </c>
+      <c r="I26" s="9" t="n">
+        <v>3645.93</v>
+      </c>
+      <c r="J26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M26" s="7" t="inlineStr"/>
+      <c r="N26" s="7" t="inlineStr"/>
+      <c r="O26" s="7" t="inlineStr"/>
+      <c r="P26" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>32925495</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>3772402</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>3772402</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="n">
+        <v>45849</v>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LAO      </t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="n">
+        <v>5856</v>
+      </c>
+      <c r="H27" s="9" t="n">
+        <v>3645.93</v>
+      </c>
+      <c r="I27" s="9" t="n">
+        <v>3645.93</v>
+      </c>
+      <c r="J27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M27" s="7" t="inlineStr"/>
+      <c r="N27" s="7" t="inlineStr"/>
+      <c r="O27" s="7" t="inlineStr"/>
+      <c r="P27" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>32925506</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>3772404</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>3772404</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="n">
+        <v>45849</v>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DON      </t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="n">
+        <v>6196</v>
+      </c>
+      <c r="H28" s="9" t="n">
+        <v>3562.52</v>
+      </c>
+      <c r="I28" s="9" t="n">
+        <v>3562.52</v>
+      </c>
+      <c r="J28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M28" s="7" t="inlineStr"/>
+      <c r="N28" s="7" t="inlineStr"/>
+      <c r="O28" s="7" t="inlineStr"/>
+      <c r="P28" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>21142496</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>2384981</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>2384981</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="n">
+        <v>45852</v>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">74673    </t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="n">
+        <v>1672</v>
+      </c>
+      <c r="H29" s="9" t="n">
+        <v>1892.81</v>
+      </c>
+      <c r="I29" s="9" t="n">
+        <v>1892.81</v>
+      </c>
+      <c r="J29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M29" s="7" t="inlineStr"/>
+      <c r="N29" s="7" t="inlineStr"/>
+      <c r="O29" s="7" t="inlineStr"/>
+      <c r="P29" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>32926256</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>3772957</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>3772957</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="n">
+        <v>45852</v>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAL      </t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="n">
+        <v>6133</v>
+      </c>
+      <c r="H30" s="9" t="n">
+        <v>3102.83</v>
+      </c>
+      <c r="I30" s="9" t="n">
+        <v>3102.83</v>
+      </c>
+      <c r="J30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M30" s="7" t="inlineStr"/>
+      <c r="N30" s="7" t="inlineStr"/>
+      <c r="O30" s="7" t="inlineStr"/>
+      <c r="P30" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>32928709</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>3774881</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>3774881</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="n">
+        <v>45856</v>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COR      </t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="n">
+        <v>5859</v>
+      </c>
+      <c r="H31" s="9" t="n">
+        <v>3562.52</v>
+      </c>
+      <c r="I31" s="9" t="n">
+        <v>3562.52</v>
+      </c>
+      <c r="J31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M31" s="7" t="inlineStr"/>
+      <c r="N31" s="7" t="inlineStr"/>
+      <c r="O31" s="7" t="inlineStr"/>
+      <c r="P31" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>32928712</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>3774882</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>3774882</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="n">
+        <v>45856</v>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAL      </t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="n">
+        <v>7094</v>
+      </c>
+      <c r="H32" s="9" t="n">
+        <v>2861.16</v>
+      </c>
+      <c r="I32" s="9" t="n">
+        <v>2861.16</v>
+      </c>
+      <c r="J32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M32" s="7" t="inlineStr"/>
+      <c r="N32" s="7" t="inlineStr"/>
+      <c r="O32" s="7" t="inlineStr"/>
+      <c r="P32" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>32928706</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>3774879</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>3774879</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="n">
+        <v>45856</v>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LAO      </t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="n">
+        <v>5858</v>
+      </c>
+      <c r="H33" s="9" t="n">
+        <v>3645.93</v>
+      </c>
+      <c r="I33" s="9" t="n">
+        <v>3645.93</v>
+      </c>
+      <c r="J33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M33" s="7" t="inlineStr"/>
+      <c r="N33" s="7" t="inlineStr"/>
+      <c r="O33" s="7" t="inlineStr"/>
+      <c r="P33" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>32928705</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>3774878</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>3774878</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="n">
+        <v>45856</v>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LAO      </t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="n">
+        <v>5857</v>
+      </c>
+      <c r="H34" s="9" t="n">
+        <v>3645.93</v>
+      </c>
+      <c r="I34" s="9" t="n">
+        <v>3645.93</v>
+      </c>
+      <c r="J34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M34" s="7" t="inlineStr"/>
+      <c r="N34" s="7" t="inlineStr"/>
+      <c r="O34" s="7" t="inlineStr"/>
+      <c r="P34" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>32928707</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>3774880</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>3774880</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="n">
+        <v>45856</v>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LAO      </t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="n">
+        <v>3221</v>
+      </c>
+      <c r="H35" s="9" t="n">
+        <v>1343.38</v>
+      </c>
+      <c r="I35" s="9" t="n">
+        <v>1343.38</v>
+      </c>
+      <c r="J35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M35" s="7" t="inlineStr"/>
+      <c r="N35" s="7" t="inlineStr"/>
+      <c r="O35" s="7" t="inlineStr"/>
+      <c r="P35" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>32931807</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>3774884</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>3774884</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="n">
+        <v>45863</v>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LAO      </t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="n">
+        <v>5860</v>
+      </c>
+      <c r="H36" s="9" t="n">
+        <v>3645.93</v>
+      </c>
+      <c r="I36" s="9" t="n">
+        <v>3645.93</v>
+      </c>
+      <c r="J36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M36" s="7" t="inlineStr"/>
+      <c r="N36" s="7" t="inlineStr"/>
+      <c r="O36" s="7" t="inlineStr"/>
+      <c r="P36" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>32931790</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>3774883</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>3774883</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="n">
+        <v>45863</v>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LAO      </t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="n">
+        <v>6321</v>
+      </c>
+      <c r="H37" s="9" t="n">
+        <v>3645.93</v>
+      </c>
+      <c r="I37" s="9" t="n">
+        <v>3645.93</v>
+      </c>
+      <c r="J37" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M37" s="7" t="inlineStr"/>
+      <c r="N37" s="7" t="inlineStr"/>
+      <c r="O37" s="7" t="inlineStr"/>
+      <c r="P37" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>32931809</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>3774885</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>3774885</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="n">
+        <v>45863</v>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DON      </t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="n">
+        <v>6209</v>
+      </c>
+      <c r="H38" s="9" t="n">
+        <v>3562.52</v>
+      </c>
+      <c r="I38" s="9" t="n">
+        <v>3562.52</v>
+      </c>
+      <c r="J38" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M38" s="7" t="inlineStr"/>
+      <c r="N38" s="7" t="inlineStr"/>
+      <c r="O38" s="7" t="inlineStr"/>
+      <c r="P38" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>32931848</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>3774886</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>3774886</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>45863</v>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAL      </t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="n">
+        <v>6134</v>
+      </c>
+      <c r="H39" s="9" t="n">
+        <v>2619.61</v>
+      </c>
+      <c r="I39" s="9" t="n">
+        <v>2619.61</v>
+      </c>
+      <c r="J39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M39" s="7" t="inlineStr"/>
+      <c r="N39" s="7" t="inlineStr"/>
+      <c r="O39" s="7" t="inlineStr"/>
+      <c r="P39" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>32935121</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>3776481</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>3776481</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="n">
+        <v>45870</v>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LAO      </t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>7245</v>
+      </c>
+      <c r="H40" s="9" t="n">
+        <v>3666.18</v>
+      </c>
+      <c r="I40" s="9" t="n">
+        <v>3666.18</v>
+      </c>
+      <c r="J40" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M40" s="7" t="inlineStr"/>
+      <c r="N40" s="7" t="inlineStr"/>
+      <c r="O40" s="7" t="inlineStr"/>
+      <c r="P40" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>32935127</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>3776484</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>3776484</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="n">
+        <v>45870</v>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LAO      </t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="n">
+        <v>1031</v>
+      </c>
+      <c r="H41" s="9" t="n">
+        <v>1575.55</v>
+      </c>
+      <c r="I41" s="9" t="n">
+        <v>1575.55</v>
+      </c>
+      <c r="J41" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M41" s="7" t="inlineStr"/>
+      <c r="N41" s="7" t="inlineStr"/>
+      <c r="O41" s="7" t="inlineStr"/>
+      <c r="P41" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>32935131</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>3776485</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>3776485</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="n">
+        <v>45870</v>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAL      </t>
+        </is>
+      </c>
+      <c r="G42" s="7" t="n">
+        <v>7492</v>
+      </c>
+      <c r="H42" s="9" t="n">
+        <v>3120.26</v>
+      </c>
+      <c r="I42" s="9" t="n">
+        <v>3120.26</v>
+      </c>
+      <c r="J42" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M42" s="7" t="inlineStr"/>
+      <c r="N42" s="7" t="inlineStr"/>
+      <c r="O42" s="7" t="inlineStr"/>
+      <c r="P42" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>32935123</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>3776482</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>3776482</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>45870</v>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LAO      </t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="n">
+        <v>8510</v>
+      </c>
+      <c r="H43" s="9" t="n">
+        <v>3666.18</v>
+      </c>
+      <c r="I43" s="9" t="n">
+        <v>3666.18</v>
+      </c>
+      <c r="J43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M43" s="7" t="inlineStr"/>
+      <c r="N43" s="7" t="inlineStr"/>
+      <c r="O43" s="7" t="inlineStr"/>
+      <c r="P43" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>32935126</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>3776483</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>3776483</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="n">
+        <v>45870</v>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LAO      </t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="n">
+        <v>5763</v>
+      </c>
+      <c r="H44" s="9" t="n">
+        <v>3666.18</v>
+      </c>
+      <c r="I44" s="9" t="n">
+        <v>3666.18</v>
+      </c>
+      <c r="J44" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M44" s="7" t="inlineStr"/>
+      <c r="N44" s="7" t="inlineStr"/>
+      <c r="O44" s="7" t="inlineStr"/>
+      <c r="P44" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>32937119</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>3776486</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>3776486</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="n">
+        <v>45877</v>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LAO      </t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="n">
+        <v>6308</v>
+      </c>
+      <c r="H45" s="9" t="n">
+        <v>3666.18</v>
+      </c>
+      <c r="I45" s="9" t="n">
+        <v>3666.18</v>
+      </c>
+      <c r="J45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M45" s="7" t="inlineStr"/>
+      <c r="N45" s="7" t="inlineStr"/>
+      <c r="O45" s="7" t="inlineStr"/>
+      <c r="P45" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>32937127</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>3776487</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>3776487</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="n">
+        <v>45877</v>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LAO      </t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="n">
+        <v>7508</v>
+      </c>
+      <c r="H46" s="9" t="n">
+        <v>3666.18</v>
+      </c>
+      <c r="I46" s="9" t="n">
+        <v>3666.18</v>
+      </c>
+      <c r="J46" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M46" s="7" t="inlineStr"/>
+      <c r="N46" s="7" t="inlineStr"/>
+      <c r="O46" s="7" t="inlineStr"/>
+      <c r="P46" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>32937133</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>3776489</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>3776489</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="n">
+        <v>45877</v>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COR      </t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="n">
+        <v>4225</v>
+      </c>
+      <c r="H47" s="9" t="n">
+        <v>3582.47</v>
+      </c>
+      <c r="I47" s="9" t="n">
+        <v>3582.47</v>
+      </c>
+      <c r="J47" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M47" s="7" t="inlineStr"/>
+      <c r="N47" s="7" t="inlineStr"/>
+      <c r="O47" s="7" t="inlineStr"/>
+      <c r="P47" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>32937135</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>3776490</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>3776490</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="n">
+        <v>45877</v>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAL      </t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="n">
+        <v>8221</v>
+      </c>
+      <c r="H48" s="9" t="n">
+        <v>3201.2</v>
+      </c>
+      <c r="I48" s="9" t="n">
+        <v>3201.2</v>
+      </c>
+      <c r="J48" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M48" s="7" t="inlineStr"/>
+      <c r="N48" s="7" t="inlineStr"/>
+      <c r="O48" s="7" t="inlineStr"/>
+      <c r="P48" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>32937131</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>3776488</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>3776488</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="n">
+        <v>45877</v>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LAO      </t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="n">
+        <v>5147</v>
+      </c>
+      <c r="H49" s="9" t="n">
+        <v>3666.18</v>
+      </c>
+      <c r="I49" s="9" t="n">
+        <v>3666.18</v>
+      </c>
+      <c r="J49" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M49" s="7" t="inlineStr"/>
+      <c r="N49" s="7" t="inlineStr"/>
+      <c r="O49" s="7" t="inlineStr"/>
+      <c r="P49" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>32938979</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>3776492</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>3776492</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="n">
+        <v>45884</v>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LAO      </t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="n">
+        <v>1055</v>
+      </c>
+      <c r="H50" s="9" t="n">
+        <v>1685.96</v>
+      </c>
+      <c r="I50" s="9" t="n">
+        <v>1685.96</v>
+      </c>
+      <c r="J50" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M50" s="7" t="inlineStr"/>
+      <c r="N50" s="7" t="inlineStr"/>
+      <c r="O50" s="7" t="inlineStr"/>
+      <c r="P50" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>32938978</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>3776491</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>3776491</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="n">
+        <v>45884</v>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LAO      </t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="n">
+        <v>6812</v>
+      </c>
+      <c r="H51" s="9" t="n">
+        <v>3666.18</v>
+      </c>
+      <c r="I51" s="9" t="n">
+        <v>3666.18</v>
+      </c>
+      <c r="J51" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M51" s="7" t="inlineStr"/>
+      <c r="N51" s="7" t="inlineStr"/>
+      <c r="O51" s="7" t="inlineStr"/>
+      <c r="P51" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>32938981</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>3776493</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>3776493</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="n">
+        <v>45884</v>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAL      </t>
+        </is>
+      </c>
+      <c r="G52" s="7" t="n">
+        <v>7207</v>
+      </c>
+      <c r="H52" s="9" t="n">
+        <v>3039.23</v>
+      </c>
+      <c r="I52" s="9" t="n">
+        <v>3039.23</v>
+      </c>
+      <c r="J52" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M52" s="7" t="inlineStr"/>
+      <c r="N52" s="7" t="inlineStr"/>
+      <c r="O52" s="7" t="inlineStr"/>
+      <c r="P52" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>32941653</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>03859420_SPL</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>3778047</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="n">
+        <v>45891</v>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAL      </t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="n">
+        <v>6816</v>
+      </c>
+      <c r="H53" s="9" t="n">
+        <v>2958.29</v>
+      </c>
+      <c r="I53" s="9" t="n">
+        <v>2958.29</v>
+      </c>
+      <c r="J53" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M53" s="7" t="inlineStr"/>
+      <c r="N53" s="7" t="inlineStr"/>
+      <c r="O53" s="7" t="inlineStr"/>
+      <c r="P53" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>32941648</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>03859414_SPL</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>3778044</t>
+        </is>
+      </c>
+      <c r="D54" s="8" t="n">
+        <v>45891</v>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LAO      </t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="n">
+        <v>6145</v>
+      </c>
+      <c r="H54" s="9" t="n">
+        <v>3666.18</v>
+      </c>
+      <c r="I54" s="9" t="n">
+        <v>3666.18</v>
+      </c>
+      <c r="J54" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M54" s="7" t="inlineStr"/>
+      <c r="N54" s="7" t="inlineStr"/>
+      <c r="O54" s="7" t="inlineStr"/>
+      <c r="P54" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>32941651</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>03859418_SPL</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>3778046</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="n">
+        <v>45891</v>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LAO      </t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="n">
+        <v>4282</v>
+      </c>
+      <c r="H55" s="9" t="n">
+        <v>2870.11</v>
+      </c>
+      <c r="I55" s="9" t="n">
+        <v>2870.11</v>
+      </c>
+      <c r="J55" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M55" s="7" t="inlineStr"/>
+      <c r="N55" s="7" t="inlineStr"/>
+      <c r="O55" s="7" t="inlineStr"/>
+      <c r="P55" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>32941228</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>03859412_SPL</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>3778043</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="n">
+        <v>45891</v>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2615     </t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="n">
+        <v>2224</v>
+      </c>
+      <c r="H56" s="9" t="n">
+        <v>1792.25</v>
+      </c>
+      <c r="I56" s="9" t="n">
+        <v>1792.25</v>
+      </c>
+      <c r="J56" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M56" s="7" t="inlineStr"/>
+      <c r="N56" s="7" t="inlineStr"/>
+      <c r="O56" s="7" t="inlineStr"/>
+      <c r="P56" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>32941656</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>03859422_SPL</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>3778048</t>
+        </is>
+      </c>
+      <c r="D57" s="8" t="n">
+        <v>45891</v>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAL      </t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="n">
+        <v>247</v>
+      </c>
+      <c r="H57" s="9" t="n">
+        <v>436.95</v>
+      </c>
+      <c r="I57" s="9" t="n">
+        <v>436.95</v>
+      </c>
+      <c r="J57" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M57" s="7" t="inlineStr"/>
+      <c r="N57" s="7" t="inlineStr"/>
+      <c r="O57" s="7" t="inlineStr"/>
+      <c r="P57" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>32941649</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>03859416_SPL</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>3778045</t>
+        </is>
+      </c>
+      <c r="D58" s="8" t="n">
+        <v>45891</v>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LAO      </t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="n">
+        <v>7694</v>
+      </c>
+      <c r="H58" s="9" t="n">
+        <v>3666.18</v>
+      </c>
+      <c r="I58" s="9" t="n">
+        <v>3666.18</v>
+      </c>
+      <c r="J58" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M58" s="7" t="inlineStr"/>
+      <c r="N58" s="7" t="inlineStr"/>
+      <c r="O58" s="7" t="inlineStr"/>
+      <c r="P58" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>32944511</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>03861611_SPL</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>3778544</t>
+        </is>
+      </c>
+      <c r="D59" s="8" t="n">
+        <v>45898</v>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LAO      </t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="n">
+        <v>5070</v>
+      </c>
+      <c r="H59" s="9" t="n">
+        <v>2870.11</v>
+      </c>
+      <c r="I59" s="9" t="n">
+        <v>2870.11</v>
+      </c>
+      <c r="J59" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M59" s="7" t="inlineStr"/>
+      <c r="N59" s="7" t="inlineStr"/>
+      <c r="O59" s="7" t="inlineStr"/>
+      <c r="P59" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>32944065</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>03859424_SPL</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>3778049</t>
+        </is>
+      </c>
+      <c r="D60" s="8" t="n">
+        <v>45898</v>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28830    </t>
+        </is>
+      </c>
+      <c r="G60" s="7" t="n">
+        <v>7719</v>
+      </c>
+      <c r="H60" s="9" t="n">
+        <v>2380.5</v>
+      </c>
+      <c r="I60" s="9" t="n">
+        <v>2380.5</v>
+      </c>
+      <c r="J60" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M60" s="7" t="inlineStr"/>
+      <c r="N60" s="7" t="inlineStr"/>
+      <c r="O60" s="7" t="inlineStr"/>
+      <c r="P60" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>32944521</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>03868942_SPL</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>3779899</t>
+        </is>
+      </c>
+      <c r="D61" s="8" t="n">
+        <v>45901</v>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAL      </t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="n">
+        <v>9092</v>
+      </c>
+      <c r="H61" s="9" t="n">
+        <v>3381.96</v>
+      </c>
+      <c r="I61" s="9" t="n">
+        <v>3381.96</v>
+      </c>
+      <c r="J61" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M61" s="7" t="inlineStr"/>
+      <c r="N61" s="7" t="inlineStr"/>
+      <c r="O61" s="7" t="inlineStr"/>
+      <c r="P61" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>32944526</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>03868944_SPL</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>3779900</t>
+        </is>
+      </c>
+      <c r="D62" s="8" t="n">
+        <v>45901</v>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAL      </t>
+        </is>
+      </c>
+      <c r="G62" s="7" t="n">
+        <v>168</v>
+      </c>
+      <c r="H62" s="9" t="n">
+        <v>223.32</v>
+      </c>
+      <c r="I62" s="9" t="n">
+        <v>223.32</v>
+      </c>
+      <c r="J62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M62" s="7" t="inlineStr"/>
+      <c r="N62" s="7" t="inlineStr"/>
+      <c r="O62" s="7" t="inlineStr"/>
+      <c r="P62" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>32948393</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>03868950_SPL</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>3779903</t>
+        </is>
+      </c>
+      <c r="D63" s="8" t="n">
+        <v>45905</v>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2615     </t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="n">
+        <v>3864</v>
+      </c>
+      <c r="H63" s="9" t="n">
+        <v>2750</v>
+      </c>
+      <c r="I63" s="9" t="n">
+        <v>2750</v>
+      </c>
+      <c r="J63" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M63" s="7" t="inlineStr"/>
+      <c r="N63" s="7" t="inlineStr"/>
+      <c r="O63" s="7" t="inlineStr"/>
+      <c r="P63" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>32948201</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>03868946_SPL</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>3779901</t>
+        </is>
+      </c>
+      <c r="D64" s="8" t="n">
+        <v>45905</v>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAL      </t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="n">
+        <v>9606</v>
+      </c>
+      <c r="H64" s="9" t="n">
+        <v>3463.34</v>
+      </c>
+      <c r="I64" s="9" t="n">
+        <v>3463.34</v>
+      </c>
+      <c r="J64" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M64" s="7" t="inlineStr"/>
+      <c r="N64" s="7" t="inlineStr"/>
+      <c r="O64" s="7" t="inlineStr"/>
+      <c r="P64" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>32948207</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>03868948_SPL</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>3779902</t>
+        </is>
+      </c>
+      <c r="D65" s="8" t="n">
+        <v>45905</v>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LAO      </t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="n">
+        <v>6863</v>
+      </c>
+      <c r="H65" s="9" t="n">
+        <v>3686.43</v>
+      </c>
+      <c r="I65" s="9" t="n">
+        <v>3686.43</v>
+      </c>
+      <c r="J65" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M65" s="7" t="inlineStr"/>
+      <c r="N65" s="7" t="inlineStr"/>
+      <c r="O65" s="7" t="inlineStr"/>
+      <c r="P65" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>32948772</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>03868952_SPL</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>3779904</t>
+        </is>
+      </c>
+      <c r="D66" s="8" t="n">
+        <v>45909</v>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28830    </t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="n">
+        <v>10075</v>
+      </c>
+      <c r="H66" s="9" t="n">
+        <v>2394</v>
+      </c>
+      <c r="I66" s="9" t="n">
+        <v>2394</v>
+      </c>
+      <c r="J66" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M66" s="7" t="inlineStr"/>
+      <c r="N66" s="7" t="inlineStr"/>
+      <c r="O66" s="7" t="inlineStr"/>
+      <c r="P66" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>32950439</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>03868954_SPL</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>3779905</t>
+        </is>
+      </c>
+      <c r="D67" s="8" t="n">
+        <v>45912</v>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28830    </t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="n">
+        <v>7500</v>
+      </c>
+      <c r="H67" s="9" t="n">
+        <v>2394</v>
+      </c>
+      <c r="I67" s="9" t="n">
+        <v>2394</v>
+      </c>
+      <c r="J67" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M67" s="7" t="inlineStr"/>
+      <c r="N67" s="7" t="inlineStr"/>
+      <c r="O67" s="7" t="inlineStr"/>
+      <c r="P67" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>32951788</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>03874544_SPL</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>3782480</t>
+        </is>
+      </c>
+      <c r="D68" s="8" t="n">
+        <v>45912</v>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LAO      </t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="n">
+        <v>22000</v>
+      </c>
+      <c r="H68" s="9" t="n">
+        <v>3686.43</v>
+      </c>
+      <c r="I68" s="9" t="n">
+        <v>3686.43</v>
+      </c>
+      <c r="J68" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M68" s="7" t="inlineStr"/>
+      <c r="N68" s="7" t="inlineStr"/>
+      <c r="O68" s="7" t="inlineStr"/>
+      <c r="P68" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>32951835</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>03868964_SPL</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>3779910</t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="n">
+        <v>45912</v>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LAO      </t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="n">
+        <v>22000</v>
+      </c>
+      <c r="H69" s="9" t="n">
+        <v>3686.43</v>
+      </c>
+      <c r="I69" s="9" t="n">
+        <v>3686.43</v>
+      </c>
+      <c r="J69" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M69" s="7" t="inlineStr"/>
+      <c r="N69" s="7" t="inlineStr"/>
+      <c r="O69" s="7" t="inlineStr"/>
+      <c r="P69" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>32951814</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>03868958_SPL</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>3779907</t>
+        </is>
+      </c>
+      <c r="D70" s="8" t="n">
+        <v>45912</v>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAL      </t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="n">
+        <v>22000</v>
+      </c>
+      <c r="H70" s="9" t="n">
+        <v>3793.94</v>
+      </c>
+      <c r="I70" s="9" t="n">
+        <v>3793.94</v>
+      </c>
+      <c r="J70" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M70" s="7" t="inlineStr"/>
+      <c r="N70" s="7" t="inlineStr"/>
+      <c r="O70" s="7" t="inlineStr"/>
+      <c r="P70" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>32951826</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>03868962_SPL</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>3779909</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="n">
+        <v>45912</v>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LAO      </t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="n">
+        <v>22000</v>
+      </c>
+      <c r="H71" s="9" t="n">
+        <v>3686.43</v>
+      </c>
+      <c r="I71" s="9" t="n">
+        <v>3686.43</v>
+      </c>
+      <c r="J71" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M71" s="7" t="inlineStr"/>
+      <c r="N71" s="7" t="inlineStr"/>
+      <c r="O71" s="7" t="inlineStr"/>
+      <c r="P71" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="inlineStr">
+        <is>
+          <t>32951590</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>03868956_SPL</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>3779906</t>
+        </is>
+      </c>
+      <c r="D72" s="8" t="n">
+        <v>45912</v>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LAO      </t>
+        </is>
+      </c>
+      <c r="G72" s="7" t="n">
+        <v>2116</v>
+      </c>
+      <c r="H72" s="9" t="n">
+        <v>1584.34</v>
+      </c>
+      <c r="I72" s="9" t="n">
+        <v>1584.34</v>
+      </c>
+      <c r="J72" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M72" s="7" t="inlineStr"/>
+      <c r="N72" s="7" t="inlineStr"/>
+      <c r="O72" s="7" t="inlineStr"/>
+      <c r="P72" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>32951816</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>03868960_SPL</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>3779908</t>
+        </is>
+      </c>
+      <c r="D73" s="8" t="n">
+        <v>45912</v>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COR      </t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="n">
+        <v>22000</v>
+      </c>
+      <c r="H73" s="9" t="n">
+        <v>3602.42</v>
+      </c>
+      <c r="I73" s="9" t="n">
+        <v>3602.42</v>
+      </c>
+      <c r="J73" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M73" s="7" t="inlineStr"/>
+      <c r="N73" s="7" t="inlineStr"/>
+      <c r="O73" s="7" t="inlineStr"/>
+      <c r="P73" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t>32958974</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>03882065_SPL</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D74" s="8" t="n">
+        <v>45915</v>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COR      </t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="n">
+        <v>8000</v>
+      </c>
+      <c r="H74" s="9" t="n">
+        <v>3602.42</v>
+      </c>
+      <c r="I74" s="9" t="n">
+        <v>3602.42</v>
+      </c>
+      <c r="J74" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M74" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="N74" s="7" t="inlineStr"/>
+      <c r="O74" s="7" t="inlineStr"/>
+      <c r="P74" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>32954897</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>03877892_SPL</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>3781862</t>
+        </is>
+      </c>
+      <c r="D75" s="8" t="n">
+        <v>45919</v>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAL      </t>
+        </is>
+      </c>
+      <c r="G75" s="7" t="n">
+        <v>8000</v>
+      </c>
+      <c r="H75" s="9" t="n">
+        <v>2893.35</v>
+      </c>
+      <c r="I75" s="9" t="n">
+        <v>2893.35</v>
+      </c>
+      <c r="J75" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M75" s="7" t="inlineStr"/>
+      <c r="N75" s="7" t="inlineStr"/>
+      <c r="O75" s="7" t="inlineStr"/>
+      <c r="P75" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>32958975</t>
+        </is>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>03882067_SPL</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D76" s="8" t="n">
+        <v>45919</v>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LAO      </t>
+        </is>
+      </c>
+      <c r="G76" s="7" t="n">
+        <v>9000</v>
+      </c>
+      <c r="H76" s="9" t="n">
+        <v>3686.43</v>
+      </c>
+      <c r="I76" s="9" t="n">
+        <v>3686.43</v>
+      </c>
+      <c r="J76" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M76" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="N76" s="7" t="inlineStr"/>
+      <c r="O76" s="7" t="inlineStr"/>
+      <c r="P76" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>32958976</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>03882069_SPL</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D77" s="8" t="n">
+        <v>45919</v>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LAO      </t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="n">
+        <v>9000</v>
+      </c>
+      <c r="H77" s="9" t="n">
+        <v>3686.43</v>
+      </c>
+      <c r="I77" s="9" t="n">
+        <v>3686.43</v>
+      </c>
+      <c r="J77" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M77" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="N77" s="7" t="inlineStr"/>
+      <c r="O77" s="7" t="inlineStr"/>
+      <c r="P77" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t>32955582</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>03877896_SPL</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="inlineStr">
+        <is>
+          <t>3781864</t>
+        </is>
+      </c>
+      <c r="D78" s="8" t="n">
+        <v>45922</v>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2615     </t>
+        </is>
+      </c>
+      <c r="G78" s="7" t="n">
+        <v>3775</v>
+      </c>
+      <c r="H78" s="9" t="n">
+        <v>2750</v>
+      </c>
+      <c r="I78" s="9" t="n">
+        <v>2750</v>
+      </c>
+      <c r="J78" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M78" s="7" t="inlineStr"/>
+      <c r="N78" s="7" t="inlineStr"/>
+      <c r="O78" s="7" t="inlineStr"/>
+      <c r="P78" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>32954009</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>03877894_SPL</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>3781863</t>
+        </is>
+      </c>
+      <c r="D79" s="8" t="n">
+        <v>45922</v>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">905 01   </t>
+        </is>
+      </c>
+      <c r="G79" s="7" t="n">
+        <v>2963</v>
+      </c>
+      <c r="H79" s="9" t="n">
+        <v>900</v>
+      </c>
+      <c r="I79" s="9" t="n">
+        <v>900</v>
+      </c>
+      <c r="J79" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" s="7" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="M79" s="7" t="inlineStr"/>
+      <c r="N79" s="7" t="inlineStr"/>
+      <c r="O79" s="7" t="inlineStr"/>
+      <c r="P79" s="7" t="inlineStr">
+        <is>
+          <t>±5%%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:P1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/output/billing_report/ebm_dinas_vergleich.xlsx
+++ b/output/billing_report/ebm_dinas_vergleich.xlsx
@@ -511,7 +511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK9"/>
+  <dimension ref="A1:AK10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -639,195 +639,207 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>AX-Cluster-Konsolidierung (Abrechnungsstrecken)</t>
+        </is>
+      </c>
+      <c r="S9" s="4" t="inlineStr">
+        <is>
+          <t>aktiv: ja  |  381 Cluster  |  0 Sub-Rows entfernt  |  7 POST-Rows nicht in AX-Datei</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Auftrags-Nr</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Master-Nr</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Sub-Nr(n)</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Anzahl Subs</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>Ist Master</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>Rech.-Nr</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>Sendungsdatum</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>Kunde</t>
         </is>
       </c>
-      <c r="J9" s="5" t="inlineStr">
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>Land</t>
         </is>
       </c>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>Empf.PLZ</t>
         </is>
       </c>
-      <c r="L9" s="5" t="inlineStr">
+      <c r="L10" s="5" t="inlineStr">
         <is>
           <t>Vers.PLZ</t>
         </is>
       </c>
-      <c r="M9" s="5" t="inlineStr">
+      <c r="M10" s="5" t="inlineStr">
         <is>
           <t>Gew.band</t>
         </is>
       </c>
-      <c r="N9" s="5" t="inlineStr">
+      <c r="N10" s="5" t="inlineStr">
         <is>
           <t>Zone</t>
         </is>
       </c>
-      <c r="O9" s="5" t="inlineStr">
+      <c r="O10" s="5" t="inlineStr">
         <is>
           <t>Basis</t>
         </is>
       </c>
-      <c r="P9" s="5" t="inlineStr">
+      <c r="P10" s="5" t="inlineStr">
         <is>
           <t>Basis Menge</t>
         </is>
       </c>
-      <c r="Q9" s="5" t="inlineStr">
+      <c r="Q10" s="5" t="inlineStr">
         <is>
           <t>Basispreis</t>
         </is>
       </c>
-      <c r="R9" s="5" t="inlineStr">
+      <c r="R10" s="5" t="inlineStr">
         <is>
           <t>Eff. Preis</t>
         </is>
       </c>
-      <c r="S9" s="5" t="inlineStr">
+      <c r="S10" s="5" t="inlineStr">
         <is>
           <t>Tonnage kg</t>
         </is>
       </c>
-      <c r="T9" s="5" t="inlineStr">
+      <c r="T10" s="5" t="inlineStr">
         <is>
           <t>Stellplätze</t>
         </is>
       </c>
-      <c r="U9" s="5" t="inlineStr">
+      <c r="U10" s="5" t="inlineStr">
         <is>
           <t>Lademeter</t>
         </is>
       </c>
-      <c r="V9" s="5" t="inlineStr">
+      <c r="V10" s="5" t="inlineStr">
         <is>
           <t>Volumen</t>
         </is>
       </c>
-      <c r="W9" s="5" t="inlineStr">
+      <c r="W10" s="5" t="inlineStr">
         <is>
           <t>Soll EUR</t>
         </is>
       </c>
-      <c r="X9" s="5" t="inlineStr">
+      <c r="X10" s="5" t="inlineStr">
         <is>
           <t>Fracht EUR</t>
         </is>
       </c>
-      <c r="Y9" s="5" t="inlineStr">
+      <c r="Y10" s="5" t="inlineStr">
         <is>
           <t>Diesel EUR</t>
         </is>
       </c>
-      <c r="Z9" s="5" t="inlineStr">
+      <c r="Z10" s="5" t="inlineStr">
         <is>
           <t>Maut EUR</t>
         </is>
       </c>
-      <c r="AA9" s="5" t="inlineStr">
+      <c r="AA10" s="5" t="inlineStr">
         <is>
           <t>Lademittel</t>
         </is>
       </c>
-      <c r="AB9" s="5" t="inlineStr">
+      <c r="AB10" s="5" t="inlineStr">
         <is>
           <t>Peak EUR</t>
         </is>
       </c>
-      <c r="AC9" s="5" t="inlineStr">
+      <c r="AC10" s="5" t="inlineStr">
         <is>
           <t>Neben EUR</t>
         </is>
       </c>
-      <c r="AD9" s="5" t="inlineStr">
+      <c r="AD10" s="5" t="inlineStr">
         <is>
           <t>EUST Zoll</t>
         </is>
       </c>
-      <c r="AE9" s="5" t="inlineStr">
+      <c r="AE10" s="5" t="inlineStr">
         <is>
           <t>Versich.</t>
         </is>
       </c>
-      <c r="AF9" s="5" t="inlineStr">
+      <c r="AF10" s="5" t="inlineStr">
         <is>
           <t>Erlöse</t>
         </is>
       </c>
-      <c r="AG9" s="5" t="inlineStr">
+      <c r="AG10" s="5" t="inlineStr">
         <is>
           <t>Abw. Grund</t>
         </is>
       </c>
-      <c r="AH9" s="5" t="inlineStr">
+      <c r="AH10" s="5" t="inlineStr">
         <is>
           <t>Komplettpreis</t>
         </is>
       </c>
-      <c r="AI9" s="5" t="inlineStr">
+      <c r="AI10" s="5" t="inlineStr">
         <is>
           <t>BI-Split</t>
         </is>
       </c>
-      <c r="AJ9" s="5" t="inlineStr">
+      <c r="AJ10" s="5" t="inlineStr">
         <is>
           <t>DINAS vs BI %</t>
         </is>
       </c>
-      <c r="AK9" s="5" t="inlineStr">
+      <c r="AK10" s="5" t="inlineStr">
         <is>
           <t>DINAS Multi-Row</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="16">
     <mergeCell ref="A3:R3"/>
     <mergeCell ref="S7:AK7"/>
     <mergeCell ref="S5:AK5"/>
@@ -835,9 +847,11 @@
     <mergeCell ref="S6:AK6"/>
     <mergeCell ref="A2:R2"/>
     <mergeCell ref="S4:AK4"/>
+    <mergeCell ref="S9:AK9"/>
     <mergeCell ref="S3:AK3"/>
     <mergeCell ref="S8:AK8"/>
     <mergeCell ref="A5:R5"/>
+    <mergeCell ref="A9:R9"/>
     <mergeCell ref="A1:AK1"/>
     <mergeCell ref="A8:R8"/>
     <mergeCell ref="A6:R6"/>
